--- a/kits/pdf-binder/samples/sds-binder/output/inventory.xlsx
+++ b/kits/pdf-binder/samples/sds-binder/output/inventory.xlsx
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="169">
   <si>
     <t>Settings used by the status formulas</t>
   </si>
@@ -118,6 +118,9 @@
     <t>Check ages as of</t>
   </si>
   <si>
+    <t>The formula =TODAY() keeps ages current each time the file is opened. Type a date to freeze them.</t>
+  </si>
+  <si>
     <t>Client / site</t>
   </si>
   <si>
@@ -127,7 +130,7 @@
     <t>Created</t>
   </si>
   <si>
-    <t>2026-10-07 10:28</t>
+    <t>2026-10-07 10:35</t>
   </si>
   <si>
     <t>No.</t>
@@ -244,6 +247,9 @@
     <t>Not named in text - check the sheet</t>
   </si>
   <si>
+    <t>1.0</t>
+  </si>
+  <si>
     <t>HALBERD-RUST-PENETRANT-SDS-2019.pdf</t>
   </si>
   <si>
@@ -256,7 +262,7 @@
     <t>Ironvale Synthetic Motor Oil 5W-30</t>
   </si>
   <si>
-    <t>Ironvale Lubricants LLC E</t>
+    <t>Ironvale Lubricants LLC</t>
   </si>
   <si>
     <t>None</t>
@@ -265,6 +271,9 @@
     <t>None found</t>
   </si>
   <si>
+    <t>None (stated on the sheet)</t>
+  </si>
+  <si>
     <t>ironvale-5w30-synthetic-sds.pdf</t>
   </si>
   <si>
@@ -286,7 +295,7 @@
     <t>Bluepeak All-Season Windshield Washer Fluid -20°F</t>
   </si>
   <si>
-    <t>Bluepeak Consumer Products Co. T</t>
+    <t>Bluepeak Consumer Products Co.</t>
   </si>
   <si>
     <t>H225, H301, H311, H331, H370</t>
@@ -319,6 +328,9 @@
     <t>Saltmarsh Coatings Ltd.</t>
   </si>
   <si>
+    <t>Revised</t>
+  </si>
+  <si>
     <t>H225, H319, H302, H332, H336, H373</t>
   </si>
   <si>
@@ -343,7 +355,7 @@
     <t>Gristmill Heavy-Duty Degreaser Concentrate</t>
   </si>
   <si>
-    <t>Gristmill Cleaning Solutions, Inc. E</t>
+    <t>Gristmill Cleaning Solutions, Inc.</t>
   </si>
   <si>
     <t>Issue date</t>
@@ -373,6 +385,9 @@
     <t>Tri-County Soap Works</t>
   </si>
   <si>
+    <t>Date prepared</t>
+  </si>
+  <si>
     <t>tri-county-hand-cleaner-msds.pdf</t>
   </si>
   <si>
@@ -448,7 +463,7 @@
     <t>Include</t>
   </si>
   <si>
-    <t>Bluepeak Consumer Products Co. T · Revised Feb 14, 2023</t>
+    <t>Bluepeak Consumer Products Co. · Revised Feb 14, 2023</t>
   </si>
   <si>
     <t>yes</t>
@@ -460,7 +475,7 @@
     <t>Halberd Tool &amp; Chemical Corp. · Revised Jun 30, 2019</t>
   </si>
   <si>
-    <t>Ironvale Lubricants LLC E · Revised Nov 22, 2024</t>
+    <t>Ironvale Lubricants LLC · Revised Nov 22, 2024</t>
   </si>
   <si>
     <t>Ridgeback · SDS requested - not yet received</t>
@@ -469,7 +484,7 @@
     <t>Saltmarsh Coatings Ltd. · Revised Feb 14, 2023</t>
   </si>
   <si>
-    <t>Gristmill Cleaning Solutions, Inc. E · Dated Aug 21, 2025</t>
+    <t>Gristmill Cleaning Solutions, Inc. · Dated Aug 21, 2025</t>
   </si>
   <si>
     <t>Tri-County Soap Works · Dated Apr 12, 2008</t>
@@ -1188,73 +1203,73 @@
   <sheetData>
     <row r="1" spans="1:23" ht="42" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -1266,16 +1281,16 @@
         <v>OK</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="5">
         <v>45730</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" s="6">
         <f>IF(ISNUMBER(E2),ROUND((Settings!$B$5-E2)/365.25,1),"")</f>
@@ -1290,31 +1305,31 @@
         <v>no</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="S2" s="2">
         <v>2</v>
@@ -1333,16 +1348,16 @@
         <v>CHECK FOR NEWER SDS</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="5">
         <v>43646</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="6">
         <f>IF(ISNUMBER(E3),ROUND((Settings!$B$5-E3)/365.25,1),"")</f>
@@ -1357,29 +1372,31 @@
         <v>YES</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="O3" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="S3" s="2">
         <v>2</v>
@@ -1398,16 +1415,16 @@
         <v>OK</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E4" s="5">
         <v>45618</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="6">
         <f>IF(ISNUMBER(E4),ROUND((Settings!$B$5-E4)/365.25,1),"")</f>
@@ -1422,27 +1439,27 @@
         <v>no</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S4" s="2">
         <v>3</v>
@@ -1482,22 +1499,22 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="7"/>
       <c r="U5" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="W5" s="8"/>
     </row>
@@ -1510,16 +1527,16 @@
         <v>REVIEW</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E6" s="5">
         <v>44971</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="6">
         <f>IF(ISNUMBER(E6),ROUND((Settings!$B$5-E6)/365.25,1),"")</f>
@@ -1534,38 +1551,38 @@
         <v>YES</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S6" s="2">
         <v>2</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="V6" s="4"/>
       <c r="W6" s="8"/>
@@ -1579,16 +1596,16 @@
         <v>CHECK FOR NEWER SDS</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E7" s="5">
         <v>44971</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G7" s="6">
         <f>IF(ISNUMBER(E7),ROUND((Settings!$B$5-E7)/365.25,1),"")</f>
@@ -1603,31 +1620,31 @@
         <v>YES</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="S7" s="2">
         <v>2</v>
@@ -1646,16 +1663,16 @@
         <v>OK</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E8" s="5">
         <v>45890</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G8" s="6">
         <f>IF(ISNUMBER(E8),ROUND((Settings!$B$5-E8)/365.25,1),"")</f>
@@ -1670,29 +1687,29 @@
         <v>no</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="S8" s="2">
         <v>3</v>
@@ -1711,16 +1728,16 @@
         <v>REPLACE: OLD FORMAT</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E9" s="5">
         <v>39550</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G9" s="6">
         <f>IF(ISNUMBER(E9),ROUND((Settings!$B$5-E9)/365.25,1),"")</f>
@@ -1737,35 +1754,35 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="S9" s="2">
         <v>1</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="W9" s="8"/>
     </row>
@@ -1777,7 +1794,7 @@
         <f>IF(V10="MISSING SDS","MISSING SDS",IF(V10="OLD MSDS FORMAT","REPLACE: OLD FORMAT",IF(T10="YES","REVIEW",IF(OR(H10="YES",I10="YES"),"CHECK FOR NEWER SDS",IF(V10="NOT ON SITE LIST","NOT ON SITE LIST","OK")))))</f>
         <v>REVIEW</v>
       </c>
-      <c r="C10" s="10"/>
+      <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="4"/>
@@ -1797,29 +1814,29 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="P10" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="Q10" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="S10" s="2">
         <v>2</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="8"/>
@@ -1833,16 +1850,16 @@
         <v>NOT ON SITE LIST</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E11" s="5">
         <v>46034</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="6">
         <f>IF(ISNUMBER(E11),ROUND((Settings!$B$5-E11)/365.25,1),"")</f>
@@ -1857,35 +1874,35 @@
         <v>no</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="S11" s="2">
         <v>2</v>
       </c>
       <c r="T11" s="7"/>
       <c r="U11" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="W11" s="8"/>
     </row>
@@ -1947,218 +1964,218 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D8" s="2">
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D9" s="2">
         <v>8</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2">
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2179,100 +2196,100 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Inventory!$B:$B,"OK")</f>
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Inventory!$B:$B,"CHECK FOR NEWER SDS")</f>
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Inventory!$B:$B,"REVIEW")</f>
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Inventory!$B:$B,"MISSING SDS")</f>
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Inventory!$B:$B,"REPLACE: OLD FORMAT")</f>
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B10" s="2">
         <f>COUNTIF(Inventory!$B:$B,"NOT ON SITE LIST")</f>
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B11" s="2">
         <f>SUM(B5:B10)</f>
@@ -2281,10 +2298,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2300,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2373,25 +2390,24 @@
         <f>TODAY()</f>
         <v>46302</v>
       </c>
-      <c r="C5" s="15">
-        <f>TODAY() keeps ages current each time the file is opened. Type a date to freeze them.</f>
-        <v>0</v>
+      <c r="C5" s="15" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2409,97 +2425,97 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="14" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="42" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="28" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="14" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="14" customHeight="1">
       <c r="A11" s="15" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="14" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="18" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="42" customHeight="1">
       <c r="A16" s="15" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="28" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="14" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="18" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="28" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="28" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="28" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/kits/pdf-binder/samples/sds-binder/output/inventory.xlsx
+++ b/kits/pdf-binder/samples/sds-binder/output/inventory.xlsx
@@ -8,14 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
-    <sheet name="Binder Index" sheetId="2" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" r:id="rId3"/>
-    <sheet name="Settings" sheetId="4" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" r:id="rId5"/>
+    <sheet name="Chemical List" sheetId="2" r:id="rId2"/>
+    <sheet name="Binder Index" sheetId="3" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" r:id="rId4"/>
+    <sheet name="Settings" sheetId="5" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Binder Index'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Binder Index'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inventory!$A$1:$W$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Chemical List'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Chemical List'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Inventory!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -98,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="174">
   <si>
     <t>Settings used by the status formulas</t>
   </si>
@@ -130,7 +133,7 @@
     <t>Created</t>
   </si>
   <si>
-    <t>2026-10-07 10:35</t>
+    <t>2026-10-07 10:36</t>
   </si>
   <si>
     <t>No.</t>
@@ -445,6 +448,21 @@
     <t>NOT ON SITE LIST</t>
   </si>
   <si>
+    <t>Hazardous chemical list</t>
+  </si>
+  <si>
+    <t>Confirmed by the employer: ______________________________     Date: ______________</t>
+  </si>
+  <si>
+    <t>Product name</t>
+  </si>
+  <si>
+    <t>SDS on file</t>
+  </si>
+  <si>
+    <t>Product names and dates are as printed on each safety data sheet. Sheets are kept in the SDS binder.</t>
+  </si>
+  <si>
     <t>Section</t>
   </si>
   <si>
@@ -577,7 +595,7 @@
     <t>6. NOT ON SITE LIST rows: ask the client whether the product is still used on site.</t>
   </si>
   <si>
-    <t>7. Send the finished list to the client to confirm. The client confirms the on-site list; you don't.</t>
+    <t>7. Send the finished list to the client to confirm. The client confirms the on-site list; you don't. The 'Chemical List' sheet is a plain printable version (it reads from the Inventory sheet).</t>
   </si>
   <si>
     <t>8. Check the 'Binder Index' sheet (titles, sections, include = yes/no), then build the binder with build_binder.py --sheet "Binder Index".</t>
@@ -1951,6 +1969,298 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <f>IF(Inventory!C2&lt;&gt;"",Inventory!C2,Inventory!O2&amp;"")</f>
+        <v>Corvane Brake Parts Cleaner (Non-Chlorinated)</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <f>Inventory!D2&amp;""</f>
+        <v>Corvane Automotive Chemicals, Inc.</v>
+      </c>
+      <c r="D6" s="4" t="str">
+        <f>Inventory!P2&amp;""</f>
+        <v>Service Bays</v>
+      </c>
+      <c r="E6" s="5">
+        <f>IF(ISNUMBER(Inventory!E2),Inventory!E2,"")</f>
+        <v>45730</v>
+      </c>
+      <c r="F6" s="7" t="str">
+        <f>IF(Inventory!R2="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <f>IF(Inventory!C3&lt;&gt;"",Inventory!C3,Inventory!O3&amp;"")</f>
+        <v>Halberd Rust Penetrant Aerosol</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <f>Inventory!D3&amp;""</f>
+        <v>Halberd Tool &amp; Chemical Corp.</v>
+      </c>
+      <c r="D7" s="4" t="str">
+        <f>Inventory!P3&amp;""</f>
+        <v>Service Bays</v>
+      </c>
+      <c r="E7" s="5">
+        <f>IF(ISNUMBER(Inventory!E3),Inventory!E3,"")</f>
+        <v>43646</v>
+      </c>
+      <c r="F7" s="7" t="str">
+        <f>IF(Inventory!R3="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="str">
+        <f>IF(Inventory!C4&lt;&gt;"",Inventory!C4,Inventory!O4&amp;"")</f>
+        <v>Ironvale Synthetic Motor Oil 5W-30</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <f>Inventory!D4&amp;""</f>
+        <v>Ironvale Lubricants LLC</v>
+      </c>
+      <c r="D8" s="4" t="str">
+        <f>Inventory!P4&amp;""</f>
+        <v>Service Bays</v>
+      </c>
+      <c r="E8" s="5">
+        <f>IF(ISNUMBER(Inventory!E4),Inventory!E4,"")</f>
+        <v>45618</v>
+      </c>
+      <c r="F8" s="7" t="str">
+        <f>IF(Inventory!R4="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <f>IF(Inventory!C5&lt;&gt;"",Inventory!C5,Inventory!O5&amp;"")</f>
+        <v>Ridgeback R-1234yf Refrigerant</v>
+      </c>
+      <c r="C9" s="4">
+        <f>Inventory!D5&amp;""</f>
+        <v/>
+      </c>
+      <c r="D9" s="4" t="str">
+        <f>Inventory!P5&amp;""</f>
+        <v>Service Bays</v>
+      </c>
+      <c r="E9" s="5">
+        <f>IF(ISNUMBER(Inventory!E5),Inventory!E5,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="7" t="str">
+        <f>IF(Inventory!R5="","MISSING","Yes")</f>
+        <v>MISSING</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="str">
+        <f>IF(Inventory!C6&lt;&gt;"",Inventory!C6,Inventory!O6&amp;"")</f>
+        <v>Bluepeak All-Season Windshield Washer Fluid -20°F</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <f>Inventory!D6&amp;""</f>
+        <v>Bluepeak Consumer Products Co.</v>
+      </c>
+      <c r="D10" s="4" t="str">
+        <f>Inventory!P6&amp;""</f>
+        <v>Service Bays</v>
+      </c>
+      <c r="E10" s="5">
+        <f>IF(ISNUMBER(Inventory!E6),Inventory!E6,"")</f>
+        <v>44971</v>
+      </c>
+      <c r="F10" s="7" t="str">
+        <f>IF(Inventory!R6="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="str">
+        <f>IF(Inventory!C7&lt;&gt;"",Inventory!C7,Inventory!O7&amp;"")</f>
+        <v>SALTMARSH AUTOMOTIVE PRIMER - GRAY</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <f>Inventory!D7&amp;""</f>
+        <v>Saltmarsh Coatings Ltd.</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f>Inventory!P7&amp;""</f>
+        <v>Paint &amp; Body Room</v>
+      </c>
+      <c r="E11" s="5">
+        <f>IF(ISNUMBER(Inventory!E7),Inventory!E7,"")</f>
+        <v>44971</v>
+      </c>
+      <c r="F11" s="7" t="str">
+        <f>IF(Inventory!R7="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="str">
+        <f>IF(Inventory!C8&lt;&gt;"",Inventory!C8,Inventory!O8&amp;"")</f>
+        <v>Gristmill Heavy-Duty Degreaser Concentrate</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <f>Inventory!D8&amp;""</f>
+        <v>Gristmill Cleaning Solutions, Inc.</v>
+      </c>
+      <c r="D12" s="4" t="str">
+        <f>Inventory!P8&amp;""</f>
+        <v>Parts Washer &amp; Storage</v>
+      </c>
+      <c r="E12" s="5">
+        <f>IF(ISNUMBER(Inventory!E8),Inventory!E8,"")</f>
+        <v>45890</v>
+      </c>
+      <c r="F12" s="7" t="str">
+        <f>IF(Inventory!R8="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="str">
+        <f>IF(Inventory!C9&lt;&gt;"",Inventory!C9,Inventory!O9&amp;"")</f>
+        <v>TRI-COUNTY HAND CLEANER W/ PUMICE</v>
+      </c>
+      <c r="C13" s="4" t="str">
+        <f>Inventory!D9&amp;""</f>
+        <v>Tri-County Soap Works</v>
+      </c>
+      <c r="D13" s="4" t="str">
+        <f>Inventory!P9&amp;""</f>
+        <v>Office &amp; Janitorial</v>
+      </c>
+      <c r="E13" s="5">
+        <f>IF(ISNUMBER(Inventory!E9),Inventory!E9,"")</f>
+        <v>39550</v>
+      </c>
+      <c r="F13" s="7" t="str">
+        <f>IF(Inventory!R9="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2">
+        <v>9</v>
+      </c>
+      <c r="B14" s="4" t="str">
+        <f>IF(Inventory!C10&lt;&gt;"",Inventory!C10,Inventory!O10&amp;"")</f>
+        <v>Pemberton Glass Cleaner</v>
+      </c>
+      <c r="C14" s="4">
+        <f>Inventory!D10&amp;""</f>
+        <v/>
+      </c>
+      <c r="D14" s="4" t="str">
+        <f>Inventory!P10&amp;""</f>
+        <v>Office &amp; Janitorial</v>
+      </c>
+      <c r="E14" s="5">
+        <f>IF(ISNUMBER(Inventory!E10),Inventory!E10,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="7" t="str">
+        <f>IF(Inventory!R10="","MISSING","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F6:F14">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"MISSING"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1964,22 +2274,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1996,10 +2306,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2016,10 +2326,10 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2036,10 +2346,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2056,10 +2366,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2074,10 +2384,10 @@
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2094,10 +2404,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2114,10 +2424,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2135,7 +2445,7 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2152,15 +2462,15 @@
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>106</v>
@@ -2172,10 +2482,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2196,7 +2506,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2209,46 +2519,46 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Inventory!$B:$B,"OK")</f>
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Inventory!$B:$B,"CHECK FOR NEWER SDS")</f>
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Inventory!$B:$B,"REVIEW")</f>
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2260,19 +2570,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Inventory!$B:$B,"REPLACE: OLD FORMAT")</f>
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2284,12 +2594,12 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B11" s="2">
         <f>SUM(B5:B10)</f>
@@ -2298,10 +2608,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="14" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2317,7 +2627,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2345,7 +2655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2415,7 +2725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2425,97 +2735,97 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="18" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="14" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="42" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="28" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="14" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="14" customHeight="1">
       <c r="A11" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="14" customHeight="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="28" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="18" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="42" customHeight="1">
       <c r="A16" s="15" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="28" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="14" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="28" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="28" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="28" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/kits/pdf-binder/samples/sds-binder/output/inventory.xlsx
+++ b/kits/pdf-binder/samples/sds-binder/output/inventory.xlsx
@@ -53,7 +53,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Found as: .</t>
+          <t>Entered by hand: read from the scanned page</t>
         </r>
       </text>
     </comment>
@@ -66,7 +66,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Not found on the sheet</t>
+          <t>Entered by hand: read from the scanned page</t>
         </r>
       </text>
     </comment>
@@ -79,7 +79,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>No date found</t>
+          <t>Entered by hand: read from the scanned page</t>
         </r>
       </text>
     </comment>
@@ -92,7 +92,20 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>.</t>
+          <t>Entered by hand: read from the scanned page</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Entered by hand: read from the scanned page</t>
         </r>
       </text>
     </comment>
@@ -101,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="179">
   <si>
     <t>Settings used by the status formulas</t>
   </si>
@@ -133,7 +146,7 @@
     <t>Created</t>
   </si>
   <si>
-    <t>2026-10-07 10:36</t>
+    <t>2026-10-07 10:49</t>
   </si>
   <si>
     <t>No.</t>
@@ -283,6 +296,9 @@
     <t>10 x 5 qt jug</t>
   </si>
   <si>
+    <t>Ridgeback</t>
+  </si>
+  <si>
     <t>Ridgeback R-1234yf Refrigerant</t>
   </si>
   <si>
@@ -409,16 +425,28 @@
     <t>OLD MSDS FORMAT</t>
   </si>
   <si>
+    <t>Pemberton Glass Cleaner</t>
+  </si>
+  <si>
+    <t>Pemberton Household Supply (fictional)</t>
+  </si>
+  <si>
+    <t>Entered by hand</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>H319</t>
+  </si>
+  <si>
     <t>pemberton-glass-cleaner.pdf</t>
   </si>
   <si>
-    <t>Pemberton Glass Cleaner</t>
-  </si>
-  <si>
     <t>6 x 32 oz spray</t>
   </si>
   <si>
-    <t>no readable text (scanned image?). Read the sheet and type the details in, or run OCR</t>
+    <t>Checked by hand (scanned sheet checked by eye); entered by hand: date, codes, product name, signal word, manufacturer</t>
   </si>
   <si>
     <t>Lanternfly Tire Shine Spray</t>
@@ -427,9 +455,6 @@
     <t>Lanternfly Car Care Co.</t>
   </si>
   <si>
-    <t>Warning</t>
-  </si>
-  <si>
     <t>H223, H229, H412</t>
   </si>
   <si>
@@ -503,6 +528,9 @@
   </si>
   <si>
     <t>Gristmill Cleaning Solutions, Inc. · Dated Aug 21, 2025</t>
+  </si>
+  <si>
+    <t>Pemberton Household Supply (fictional) · Revised Sep 3, 2024</t>
   </si>
   <si>
     <t>Tri-County Soap Works · Dated Apr 12, 2008</t>
@@ -736,7 +764,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -783,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -817,6 +845,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1496,7 +1527,9 @@
         <v>MISSING SDS</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="D5" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="6">
@@ -1517,22 +1550,22 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>43</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="7"/>
       <c r="U5" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W5" s="8"/>
     </row>
@@ -1545,10 +1578,10 @@
         <v>REVIEW</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" s="5">
         <v>44971</v>
@@ -1572,35 +1605,35 @@
         <v>37</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>43</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S6" s="2">
         <v>2</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V6" s="4"/>
       <c r="W6" s="8"/>
@@ -1614,16 +1647,16 @@
         <v>CHECK FOR NEWER SDS</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="5">
         <v>44971</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="6">
         <f>IF(ISNUMBER(E7),ROUND((Settings!$B$5-E7)/365.25,1),"")</f>
@@ -1641,28 +1674,28 @@
         <v>37</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="S7" s="2">
         <v>2</v>
@@ -1681,16 +1714,16 @@
         <v>OK</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" s="5">
         <v>45890</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8" s="6">
         <f>IF(ISNUMBER(E8),ROUND((Settings!$B$5-E8)/365.25,1),"")</f>
@@ -1708,26 +1741,26 @@
         <v>37</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="S8" s="2">
         <v>3</v>
@@ -1746,16 +1779,16 @@
         <v>REPLACE: OLD FORMAT</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9" s="5">
         <v>39550</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G9" s="6">
         <f>IF(ISNUMBER(E9),ROUND((Settings!$B$5-E9)/365.25,1),"")</f>
@@ -1779,28 +1812,28 @@
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="S9" s="2">
         <v>1</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="W9" s="8"/>
     </row>
@@ -1810,27 +1843,41 @@
       </c>
       <c r="B10" s="3" t="str">
         <f>IF(V10="MISSING SDS","MISSING SDS",IF(V10="OLD MSDS FORMAT","REPLACE: OLD FORMAT",IF(T10="YES","REVIEW",IF(OR(H10="YES",I10="YES"),"CHECK FOR NEWER SDS",IF(V10="NOT ON SITE LIST","NOT ON SITE LIST","OK")))))</f>
-        <v>REVIEW</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="4"/>
+        <v>OK</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="12">
+        <v>45538</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="G10" s="6">
         <f>IF(ISNUMBER(E10),ROUND((Settings!$B$5-E10)/365.25,1),"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="H10" s="7" t="str">
         <f>IF(ISNUMBER(E10),IF((Settings!$B$5-E10)/365.25&gt;Settings!$B$3,"YES","no"),"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="7">
+        <v>no</v>
+      </c>
+      <c r="I10" s="7" t="str">
         <f>IF(AND(ISNUMBER(E10),ISNUMBER(Settings!$B$4)),IF(E10&lt;Settings!$B$4,"YES","no"),"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+        <v>no</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="M10" s="9" t="s">
         <v>48</v>
       </c>
@@ -1839,22 +1886,20 @@
         <v>103</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="S10" s="2">
         <v>2</v>
       </c>
-      <c r="T10" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="T10" s="7"/>
       <c r="U10" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="8"/>
@@ -1868,10 +1913,10 @@
         <v>NOT ON SITE LIST</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E11" s="5">
         <v>46034</v>
@@ -1892,35 +1937,35 @@
         <v>no</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="S11" s="2">
         <v>2</v>
       </c>
       <c r="T11" s="7"/>
       <c r="U11" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="W11" s="8"/>
     </row>
@@ -1984,18 +2029,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
-        <v>115</v>
+      <c r="A1" s="13" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="14" t="s">
-        <v>116</v>
+      <c r="A3" s="15" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2003,7 +2048,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -2015,7 +2060,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2101,9 +2146,9 @@
         <f>IF(Inventory!C5&lt;&gt;"",Inventory!C5,Inventory!O5&amp;"")</f>
         <v>Ridgeback R-1234yf Refrigerant</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="4" t="str">
         <f>Inventory!D5&amp;""</f>
-        <v/>
+        <v>Ridgeback</v>
       </c>
       <c r="D9" s="4" t="str">
         <f>Inventory!P5&amp;""</f>
@@ -2226,9 +2271,9 @@
         <f>IF(Inventory!C10&lt;&gt;"",Inventory!C10,Inventory!O10&amp;"")</f>
         <v>Pemberton Glass Cleaner</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="4" t="str">
         <f>Inventory!D10&amp;""</f>
-        <v/>
+        <v>Pemberton Household Supply (fictional)</v>
       </c>
       <c r="D14" s="4" t="str">
         <f>Inventory!P10&amp;""</f>
@@ -2236,7 +2281,7 @@
       </c>
       <c r="E14" s="5">
         <f>IF(ISNUMBER(Inventory!E10),Inventory!E10,"")</f>
-        <v/>
+        <v>45538</v>
       </c>
       <c r="F14" s="7" t="str">
         <f>IF(Inventory!R10="","MISSING","Yes")</f>
@@ -2244,8 +2289,8 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="13" t="s">
-        <v>119</v>
+      <c r="A16" s="14" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2274,22 +2319,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2297,19 +2342,19 @@
         <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2326,10 +2371,10 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2346,10 +2391,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2366,10 +2411,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2377,115 +2422,117 @@
         <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2">
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D9" s="2">
         <v>8</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="F9" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="2">
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2505,12 +2552,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
-        <v>138</v>
+      <c r="A1" s="13" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2519,87 +2566,87 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF(Inventory!$B:$B,"OK")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF(Inventory!$B:$B,"CHECK FOR NEWER SDS")</f>
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF(Inventory!$B:$B,"REVIEW")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF(Inventory!$B:$B,"MISSING SDS")</f>
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF(Inventory!$B:$B,"REPLACE: OLD FORMAT")</f>
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B10" s="2">
         <f>COUNTIF(Inventory!$B:$B,"NOT ON SITE LIST")</f>
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B11" s="2">
         <f>SUM(B5:B10)</f>
@@ -2607,15 +2654,15 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="14" t="s">
-        <v>152</v>
+      <c r="A13" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="15" t="s">
         <v>1</v>
       </c>
       <c r="B14">
@@ -2623,11 +2670,11 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2666,57 +2713,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>3</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="17">
         <v>45492</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="17">
         <f>TODAY()</f>
         <v>46302</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2734,98 +2781,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
-        <v>155</v>
+      <c r="A1" s="13" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28" customHeight="1">
-      <c r="A3" s="15" t="s">
-        <v>156</v>
+      <c r="A3" s="16" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="18" t="s">
-        <v>157</v>
+      <c r="A5" s="19" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="14" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>158</v>
+      <c r="A6" s="16" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="42" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>159</v>
+      <c r="A7" s="16" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="28" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>160</v>
+      <c r="A8" s="16" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="14" customHeight="1">
-      <c r="A9" s="15" t="s">
-        <v>161</v>
+      <c r="A9" s="16" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="14" customHeight="1">
-      <c r="A10" s="15" t="s">
-        <v>162</v>
+      <c r="A10" s="16" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="14" customHeight="1">
-      <c r="A11" s="15" t="s">
-        <v>163</v>
+      <c r="A11" s="16" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="28" customHeight="1">
-      <c r="A12" s="15" t="s">
-        <v>164</v>
+      <c r="A12" s="16" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="28" customHeight="1">
-      <c r="A13" s="15" t="s">
-        <v>165</v>
+      <c r="A13" s="16" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="18" t="s">
-        <v>166</v>
+      <c r="A15" s="19" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="42" customHeight="1">
-      <c r="A16" s="15" t="s">
-        <v>167</v>
+      <c r="A16" s="16" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="28" customHeight="1">
-      <c r="A17" s="15" t="s">
-        <v>168</v>
+      <c r="A17" s="16" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="14" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>169</v>
+      <c r="A18" s="16" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="18" t="s">
-        <v>170</v>
+      <c r="A20" s="19" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="28" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>171</v>
+      <c r="A21" s="16" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="28" customHeight="1">
-      <c r="A22" s="15" t="s">
-        <v>172</v>
+      <c r="A22" s="16" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="28" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>173</v>
+      <c r="A23" s="16" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
